--- a/erp-server/erp-server-plm/src/main/resources/excel/productPlan.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productPlan.xlsx
@@ -264,22 +264,22 @@
     <t>{.salesPlatformName}</t>
   </si>
   <si>
-    <t>{.priceCny}</t>
-  </si>
-  <si>
-    <t>{.priceUsd}</t>
-  </si>
-  <si>
-    <t>{.isNeedIDDesign}</t>
-  </si>
-  <si>
-    <t>{.isNeedStructuralDesign}</t>
-  </si>
-  <si>
-    <t>{.targetCost}</t>
-  </si>
-  <si>
-    <t>{.estimatedMoldCost}</t>
+    <t>{.priceCnyStr}</t>
+  </si>
+  <si>
+    <t>{.priceUsdStr}</t>
+  </si>
+  <si>
+    <t>{.isNeedIDDesignStr}</t>
+  </si>
+  <si>
+    <t>{.isNeedStructuralDesignStr}</t>
+  </si>
+  <si>
+    <t>{.targetCostStr}</t>
+  </si>
+  <si>
+    <t>{.estimatedMoldCostStr}</t>
   </si>
   <si>
     <t>{.supplierStatus}</t>
@@ -300,7 +300,7 @@
     <t>{.planFirstMassStockInDateStr}</t>
   </si>
   <si>
-    <t>{.planMarketingSeason}</t>
+    <t>{.planMarketingSeasonName}</t>
   </si>
   <si>
     <t>{.planListingDateStr}</t>
@@ -339,10 +339,10 @@
     <t>{.novemberAmountStr}</t>
   </si>
   <si>
-    <t>{.decemberAmountStrNo}</t>
-  </si>
-  <si>
-    <t>{.januaryQtyStrNo}</t>
+    <t>{.decemberAmountStr}</t>
+  </si>
+  <si>
+    <t>{.januaryQtyStr}</t>
   </si>
   <si>
     <t>{.februaryQtyStr}</t>
@@ -357,7 +357,7 @@
     <t>{.mayQtyStr}</t>
   </si>
   <si>
-    <t>{.juneQtyStrNo}</t>
+    <t>{.juneQtyStr}</t>
   </si>
   <si>
     <t>{.julyQtyStr}</t>
@@ -366,10 +366,10 @@
     <t>{.augustQtyStr}</t>
   </si>
   <si>
-    <t>{.septemberQtyStrNo}</t>
-  </si>
-  <si>
-    <t>{.octoberQtyStrNo}</t>
+    <t>{.septemberQtyStr}</t>
+  </si>
+  <si>
+    <t>{.octoberQtyStr}</t>
   </si>
   <si>
     <t>{.novemberQtyStr}</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productPlan.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productPlan.xlsx
@@ -201,7 +201,7 @@
     <t>错误信息</t>
   </si>
   <si>
-    <t>{.year}</t>
+    <t>{.yearStr}</t>
   </si>
   <si>
     <t>{.chargeName}</t>
@@ -394,7 +394,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,7 +404,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -877,10 +891,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -889,37 +903,31 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -928,105 +936,117 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1379,374 +1399,377 @@
   <sheetPr/>
   <dimension ref="A1:BI2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="61" max="61" width="13.625" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:61">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:61">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Z2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AA2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AD2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AE2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AF2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AG2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AH2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AI2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AK2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AL2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AM2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AN2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AO2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AP2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AR2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AS2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AT2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AU2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AV2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AW2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AX2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="AY2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BA2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BB2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BC2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BD2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BE2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BF2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BG2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BH2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BI2" s="4" t="s">
         <v>121</v>
       </c>
     </row>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productPlan.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productPlan.xlsx
@@ -36,13 +36,13 @@
     <t>产品款品</t>
   </si>
   <si>
-    <t>新品/老品</t>
+    <t>新品/老品升级</t>
   </si>
   <si>
     <t>三代规划（721原则）</t>
   </si>
   <si>
-    <t>产品名称</t>
+    <t>产品名称（中文）</t>
   </si>
   <si>
     <t>产品名称（英文）</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productPlan.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productPlan.xlsx
@@ -123,76 +123,76 @@
     <t>计划上市时间</t>
   </si>
   <si>
-    <t>一月销售额</t>
-  </si>
-  <si>
-    <t>二月销售额</t>
-  </si>
-  <si>
-    <t>三月销售额</t>
-  </si>
-  <si>
-    <t>四月销售额</t>
-  </si>
-  <si>
-    <t>五月销售额</t>
-  </si>
-  <si>
-    <t>六月销售额</t>
-  </si>
-  <si>
-    <t>七月销售额</t>
-  </si>
-  <si>
-    <t>八月销售额</t>
-  </si>
-  <si>
-    <t>九月销售额</t>
-  </si>
-  <si>
-    <t>十月销售额</t>
-  </si>
-  <si>
-    <t>十一月销售额</t>
-  </si>
-  <si>
-    <t>十二月销售额</t>
-  </si>
-  <si>
-    <t>一月销量</t>
-  </si>
-  <si>
-    <t>二月销量</t>
-  </si>
-  <si>
-    <t>三月销量</t>
-  </si>
-  <si>
-    <t>四月销量</t>
-  </si>
-  <si>
-    <t>五月销量</t>
-  </si>
-  <si>
-    <t>六月销量</t>
-  </si>
-  <si>
-    <t>七月销量</t>
-  </si>
-  <si>
-    <t>八月销量</t>
-  </si>
-  <si>
-    <t>九月销量</t>
-  </si>
-  <si>
-    <t>十月销量</t>
-  </si>
-  <si>
-    <t>十一月销量</t>
-  </si>
-  <si>
-    <t>十二月销量</t>
+    <t>1月销售额</t>
+  </si>
+  <si>
+    <t>2月销售额</t>
+  </si>
+  <si>
+    <t>3月销售额</t>
+  </si>
+  <si>
+    <t>4月销售额</t>
+  </si>
+  <si>
+    <t>5月销售额</t>
+  </si>
+  <si>
+    <t>6月销售额</t>
+  </si>
+  <si>
+    <t>7月销售额</t>
+  </si>
+  <si>
+    <t>8月销售额</t>
+  </si>
+  <si>
+    <t>9月销售额</t>
+  </si>
+  <si>
+    <t>10月销售额</t>
+  </si>
+  <si>
+    <t>11月销售额</t>
+  </si>
+  <si>
+    <t>12月销售额</t>
+  </si>
+  <si>
+    <t>1月销量</t>
+  </si>
+  <si>
+    <t>2月销量</t>
+  </si>
+  <si>
+    <t>3月销量</t>
+  </si>
+  <si>
+    <t>4月销量</t>
+  </si>
+  <si>
+    <t>5月销量</t>
+  </si>
+  <si>
+    <t>6月销量</t>
+  </si>
+  <si>
+    <t>7月销量</t>
+  </si>
+  <si>
+    <t>8月销量</t>
+  </si>
+  <si>
+    <t>9月销量</t>
+  </si>
+  <si>
+    <t>10月销量</t>
+  </si>
+  <si>
+    <t>11月销量</t>
+  </si>
+  <si>
+    <t>12月销量</t>
   </si>
   <si>
     <t>其他备注</t>
